--- a/Action/Data/CSV/Stage/Stage.xlsx
+++ b/Action/Data/CSV/Stage/Stage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99255174-29B3-448F-8CD9-585880B2C5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B67300F-7B6D-41BE-9D3C-B902C7B01EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="2940" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -5453,17 +5453,17 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J96">
         <f t="shared" si="36"/>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="K96">
         <f t="shared" si="37"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="L96">
         <f t="shared" si="38"/>
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="M96">
         <v>0</v>

--- a/Action/Data/CSV/Stage/Stage.xlsx
+++ b/Action/Data/CSV/Stage/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B67300F-7B6D-41BE-9D3C-B902C7B01EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6050DC03-B644-4618-A604-ABEB17098F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="B96">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -5453,17 +5453,17 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J96">
         <f t="shared" si="36"/>
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="K96">
         <f t="shared" si="37"/>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="L96">
         <f t="shared" si="38"/>
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -5488,19 +5488,19 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -5541,19 +5541,19 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -5597,10 +5597,10 @@
         <v>0</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>-340</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -5650,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>-1080</v>
       </c>
       <c r="D100">
         <v>0</v>

--- a/Action/Data/CSV/Stage/Stage.xlsx
+++ b/Action/Data/CSV/Stage/Stage.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Documents\GitHub\GameProject\Action\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6050DC03-B644-4618-A604-ABEB17098F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A01B760-C1D4-44F5-AAB6-54603E591E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Stage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -393,12 +396,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BFE65-1919-4E86-A258-49B12076C0A7}">
   <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="16" width="5.625" customWidth="1"/>
+    <col min="1" max="16" width="5.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A1">
         <v>0</v>
       </c>
@@ -451,7 +454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>0</v>
       </c>
@@ -504,7 +507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>0</v>
       </c>
@@ -557,7 +560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>0</v>
       </c>
@@ -610,7 +613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>0</v>
       </c>
@@ -663,7 +666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>0</v>
       </c>
@@ -716,7 +719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>0</v>
       </c>
@@ -769,7 +772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>20</v>
       </c>
@@ -822,7 +825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>0</v>
       </c>
@@ -875,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>-20</v>
       </c>
@@ -928,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>-40</v>
       </c>
@@ -981,7 +984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>-60</v>
       </c>
@@ -1034,7 +1037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>-80</v>
       </c>
@@ -1087,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>-100</v>
       </c>
@@ -1140,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>-120</v>
       </c>
@@ -1193,7 +1196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>-140</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>-160</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>-180</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>-200</v>
       </c>
@@ -1405,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>-180</v>
       </c>
@@ -1458,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>-180</v>
       </c>
@@ -1511,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>-180</v>
       </c>
@@ -1564,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>-180</v>
       </c>
@@ -1617,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>-180</v>
       </c>
@@ -1670,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>-200</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>-180</v>
       </c>
@@ -1776,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>-160</v>
       </c>
@@ -1829,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>-140</v>
       </c>
@@ -1882,7 +1885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>-120</v>
       </c>
@@ -1935,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>-100</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>-60</v>
       </c>
@@ -2041,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>-40</v>
       </c>
@@ -2094,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>-20</v>
       </c>
@@ -2147,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>20</v>
       </c>
@@ -2200,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>40</v>
       </c>
@@ -2253,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>60</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>100</v>
       </c>
@@ -2359,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>120</v>
       </c>
@@ -2412,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>140</v>
       </c>
@@ -2465,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>180</v>
       </c>
@@ -2518,7 +2521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>200</v>
       </c>
@@ -2571,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>220</v>
       </c>
@@ -2624,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>260</v>
       </c>
@@ -2677,7 +2680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>260</v>
       </c>
@@ -2730,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>260</v>
       </c>
@@ -2783,7 +2786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>260</v>
       </c>
@@ -2836,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>260</v>
       </c>
@@ -2889,7 +2892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>260</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>260</v>
       </c>
@@ -2995,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>260</v>
       </c>
@@ -3048,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>260</v>
       </c>
@@ -3101,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>340</v>
       </c>
@@ -3154,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>340</v>
       </c>
@@ -3207,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>340</v>
       </c>
@@ -3260,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>420</v>
       </c>
@@ -3313,7 +3316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>420</v>
       </c>
@@ -3366,7 +3369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>420</v>
       </c>
@@ -3419,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>420</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>420</v>
       </c>
@@ -3525,7 +3528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>420</v>
       </c>
@@ -3578,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>420</v>
       </c>
@@ -3631,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>420</v>
       </c>
@@ -3684,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>420</v>
       </c>
@@ -3737,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>420</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>420</v>
       </c>
@@ -3843,7 +3846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>360</v>
       </c>
@@ -3896,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>120</v>
       </c>
@@ -3949,7 +3952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>100</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>80</v>
       </c>
@@ -4055,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>40</v>
       </c>
@@ -4108,7 +4111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>40</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>0</v>
       </c>
@@ -4214,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>0</v>
       </c>
@@ -4267,7 +4270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>0</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>0</v>
       </c>
@@ -4373,7 +4376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>0</v>
       </c>
@@ -4426,7 +4429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>0</v>
       </c>
@@ -4479,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>0</v>
       </c>
@@ -4532,7 +4535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>0</v>
       </c>
@@ -4585,7 +4588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>0</v>
       </c>
@@ -4638,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>0</v>
       </c>
@@ -4691,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>40</v>
       </c>
@@ -4744,7 +4747,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>-40</v>
       </c>
@@ -4797,7 +4800,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>0</v>
       </c>
@@ -4850,7 +4853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>0</v>
       </c>
@@ -4903,7 +4906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>0</v>
       </c>
@@ -4956,7 +4959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>60</v>
       </c>
@@ -5009,7 +5012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>-60</v>
       </c>
@@ -5062,7 +5065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>0</v>
       </c>
@@ -5115,7 +5118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>0</v>
       </c>
@@ -5168,12 +5171,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>0</v>
       </c>
       <c r="B91">
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="C91">
         <v>560</v>
@@ -5191,7 +5194,7 @@
         <v>15</v>
       </c>
       <c r="H91">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I91">
         <v>5</v>
@@ -5202,7 +5205,7 @@
       </c>
       <c r="K91">
         <f t="shared" si="37"/>
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="L91">
         <f t="shared" si="38"/>
@@ -5221,12 +5224,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>120</v>
       </c>
       <c r="B92">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="C92">
         <v>440</v>
@@ -5265,7 +5268,7 @@
         <v>-120</v>
       </c>
       <c r="N92">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="O92">
         <v>440</v>
@@ -5274,12 +5277,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>-120</v>
       </c>
       <c r="B93">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="C93">
         <v>460</v>
@@ -5318,21 +5321,21 @@
         <v>120</v>
       </c>
       <c r="N93">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="O93">
         <v>460</v>
       </c>
       <c r="P93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>120</v>
       </c>
       <c r="B94">
-        <v>1150</v>
+        <v>1120</v>
       </c>
       <c r="C94">
         <v>480</v>
@@ -5371,21 +5374,21 @@
         <v>-120</v>
       </c>
       <c r="N94">
-        <v>1150</v>
+        <v>1120</v>
       </c>
       <c r="O94">
         <v>480</v>
       </c>
       <c r="P94">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>0</v>
       </c>
       <c r="B95">
-        <v>1200</v>
+        <v>1140</v>
       </c>
       <c r="C95">
         <v>640</v>
@@ -5433,7 +5436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>0</v>
       </c>
@@ -5486,7 +5489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>200</v>
       </c>
@@ -5539,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>100</v>
       </c>
@@ -5592,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>0</v>
       </c>
@@ -5645,7 +5648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>0</v>
       </c>
